--- a/files/excel/IFINCOLL/GL link.xlsx
+++ b/files/excel/IFINCOLL/GL link.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Danu\Documents\RPAAutomation\files\excel\IFINCOLL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{627DBE7C-8AD1-4423-A7AC-E041FD700085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C883139-90DE-474D-B0A9-9B8C05250002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
